--- a/team_skill_matrix.xlsx
+++ b/team_skill_matrix.xlsx
@@ -18,9 +18,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Capability Overview'!$A$4:$F$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Delivery Capacity'!$A$4:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Skill Matrix'!$A$4:$J$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Skill Matrix'!$A$4:$J$262</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Skill Matrix'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Skill Library'!$A$1:$C$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Skill Library'!$A$1:$C$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Projects'!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -311,8 +311,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SkillMatrixTable" displayName="SkillMatrixTable" ref="A4:J244" headerRowCount="1">
-  <autoFilter ref="A4:J244"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SkillMatrixTable" displayName="SkillMatrixTable" ref="A4:J262" headerRowCount="1">
+  <autoFilter ref="A4:J262"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Employee"/>
     <tableColumn id="2" name="Experience"/>
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -702,8 +702,12 @@
 API: RESTful APIs
 Cloud / AWS: AWS S3, AWS Knowledge
 DevOps: CI/CD Pipeline Creation
+Mobile: React Native
+Desktop: Electron.js
+Frameworks: Angular, JavaScript / TypeScript Frameworks &amp; Libraries
 Tools: Git
 Architecture: System Design
+Delivery: End-to-End Frontend &amp; Backend Delivery, Application Deployment
 Common Foundation: GitHub, HTML, CSS</t>
         </is>
       </c>
@@ -721,20 +725,55 @@
     <row r="6" ht="92" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>MD Salman</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>5+ years</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Frontend Developer (React.js)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Frontend: React.js, JavaScript, TypeScript, HTML, CSS, Responsive UI Development, Frontend System Architecture
+Tools: Git
+Delivery: Web Application Development
+Common Foundation: GitHub</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Full-stack product delivery and engineering support</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Role-based starter profile; validate detailed ratings before client submission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
           <t>Kajal Mahapatra</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>7.2+ years</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Backend Expert (Node.js)</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Product Management: Product Discovery, PRD &amp; API Contract Writing, Workflow Orchestration, Sprint Planning, Backlog Grooming, Stakeholder Management
 Leadership: Cross-functional Leadership, Team Mentoring
@@ -753,34 +792,34 @@
 Common Foundation: GitHub, HTML, CSS, TypeScript</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Full-stack product delivery and engineering support</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Skills and projects incorporated from the supplied profile workbook.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="92" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="92" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Subham Sahoo</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>5.5+ years</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Frontend: React.js, Next.js
 Backend: Node.js, Express.js, FastAPI
@@ -788,39 +827,40 @@
 Database: PostgreSQL, MongoDB
 API: RESTful APIs
 AI: AI / LLM APIs
+Mobile: React Native
 Tools: Git
 Architecture: System Design
 Common Foundation: GitHub, HTML, CSS</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Full-stack product delivery and engineering support</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Role-based starter profile; validate detailed ratings before client submission.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="92" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9" ht="92" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Gautam Kumar</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>4+ years</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Frontend: React.js, Next.js
 Backend: Node.js, Express.js
@@ -832,73 +872,74 @@
 Common Foundation: GitHub, HTML, CSS</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Full-stack product delivery and engineering support</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Role-based starter profile; validate detailed ratings before client submission.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="92" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10" ht="92" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Rajat Mahapatra</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>2+ years</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Frontend: Next.js, React.js
 Languages: JavaScript, TypeScript
 Backend: Node.js, Express.js
 Database: PostgreSQL, MongoDB
 API: RESTful APIs
+Mobile: React Native
 Tools: Git
 Deployment: Vercel
 Common Foundation: GitHub, HTML, CSS</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Full-stack product delivery and engineering support</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Role-based starter profile; validate detailed ratings before client submission.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="92" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11" ht="92" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Sohail amjad</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>6+ years</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Frontend: Angular, TypeScript, JavaScript, HTML5, CSS / SCSS, RxJS, NgRx, Angular Material, PrimeNG
 Architecture: Micro Frontend, Module Federation, System Design
@@ -912,34 +953,34 @@
 Common Foundation: GitHub, HTML, CSS</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Full-stack product delivery and engineering support</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Skills and projects incorporated from the supplied profile workbook.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="92" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12" ht="92" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Suraj Sharma</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>6+ years</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>ServiceNow Consultant</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>ServiceNow ITAM: SAM Pro, AICT, Asset Lifecycle Management
 SAM Implementation: Implementation &amp; Migration
@@ -951,34 +992,34 @@
 Reporting: Dashboards &amp; Reporting</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>ServiceNow consulting, ITSM workflows and business process delivery</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Role-based starter profile; validate detailed ratings before client submission.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="92" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="13" ht="92" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Swhetha Talreja</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>4+ years</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Project Management and Digital Marketing Expert</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Project Management: Project Planning, Sprint Planning, Backlog Grooming, Risk Management
 Leadership: Stakeholder Management, Team Coordination
@@ -989,12 +1030,12 @@
 Common Foundation: GitHub, HTML, CSS, JavaScript, TypeScript</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Project coordination, planning, stakeholder and marketing support</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Role-based starter profile; validate detailed ratings before client submission.</t>
         </is>
@@ -1151,7 +1192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J244"/>
+  <dimension ref="A1:J262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1940,12 +1981,12 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="F20" s="14" t="n">
@@ -1986,12 +2027,12 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>System Design</t>
+          <t>Electron.js</t>
         </is>
       </c>
       <c r="F21" s="11" t="n">
@@ -2032,16 +2073,16 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Frameworks</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <f>IF(F22="","",CHOOSE(F22,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2052,7 +2093,7 @@
         <v/>
       </c>
       <c r="I22" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
@@ -2078,16 +2119,16 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Frameworks</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JavaScript / TypeScript Frameworks &amp; Libraries</t>
         </is>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" s="11">
         <f>IF(F23="","",CHOOSE(F23,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2098,7 +2139,7 @@
         <v/>
       </c>
       <c r="I23" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
@@ -2124,16 +2165,16 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="14">
         <f>IF(F24="","",CHOOSE(F24,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2144,7 +2185,7 @@
         <v/>
       </c>
       <c r="I24" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24" s="13" t="inlineStr">
         <is>
@@ -2155,27 +2196,27 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>Amit Kumar</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Full Stack Developer (React, Node.js, Next.js)</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Product Discovery</t>
+          <t>System Design</t>
         </is>
       </c>
       <c r="F25" s="11" t="n">
@@ -2194,34 +2235,34 @@
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Hands-on product discovery and requirement translation</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>Amit Kumar</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Full Stack Developer (React, Node.js, Next.js)</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>PRD &amp; API Contract Writing</t>
+          <t>End-to-End Frontend &amp; Backend Delivery</t>
         </is>
       </c>
       <c r="F26" s="14" t="n">
@@ -2240,34 +2281,34 @@
       </c>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>Authors API contracts and technical documentation</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>Amit Kumar</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Full Stack Developer (React, Node.js, Next.js)</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Workflow Orchestration</t>
+          <t>Application Deployment</t>
         </is>
       </c>
       <c r="F27" s="11" t="n">
@@ -2286,38 +2327,38 @@
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>Translates complex enterprise workflows into technical flows</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>Amit Kumar</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Full Stack Developer (React, Node.js, Next.js)</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Sprint Planning</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <f>IF(F28="","",CHOOSE(F28,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2328,42 +2369,42 @@
         <v/>
       </c>
       <c r="I28" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>Drives sprint planning and Agile delivery</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>Amit Kumar</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Full Stack Developer (React, Node.js, Next.js)</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Backlog Grooming</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G29" s="11">
         <f>IF(F29="","",CHOOSE(F29,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2374,42 +2415,42 @@
         <v/>
       </c>
       <c r="I29" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>Experience coordinating backlog and feature velocity</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>Amit Kumar</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Full Stack Developer (React, Node.js, Next.js)</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Stakeholder Management</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
         <f>IF(F30="","",CHOOSE(F30,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2420,42 +2461,42 @@
         <v/>
       </c>
       <c r="I30" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>Works with business, engineering and non-technical stakeholders</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5+ years</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Frontend Developer (React.js)</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Cross-functional Leadership</t>
+          <t>React.js</t>
         </is>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="11">
         <f>IF(F31="","",CHOOSE(F31,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2470,38 +2511,38 @@
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>Technical bridge between business and engineering teams</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5+ years</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Frontend Developer (React.js)</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Team Mentoring</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" s="14">
         <f>IF(F32="","",CHOOSE(F32,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2516,38 +2557,38 @@
       </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>Led backend team and mentored developers</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5+ years</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Frontend Developer (React.js)</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Node.js</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G33" s="11">
         <f>IF(F33="","",CHOOSE(F33,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2562,34 +2603,34 @@
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>Core backend technology across multiple roles/projects</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5+ years</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Frontend Developer (React.js)</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Express.js</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="F34" s="14" t="n">
@@ -2608,34 +2649,34 @@
       </c>
       <c r="J34" s="13" t="inlineStr">
         <is>
-          <t>RESTful API and backend service development</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5+ years</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Frontend Developer (React.js)</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>RESTful APIs</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="F35" s="11" t="n">
@@ -2654,38 +2695,38 @@
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Extensive API design, development and integration</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5+ years</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Frontend Developer (React.js)</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Microservices Architecture</t>
+          <t>Responsive UI Development</t>
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="14">
         <f>IF(F36="","",CHOOSE(F36,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2700,24 +2741,24 @@
       </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>Designed scalable modular microservices</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5+ years</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Frontend Developer (React.js)</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -2727,7 +2768,7 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>React.js</t>
+          <t>Frontend System Architecture</t>
         </is>
       </c>
       <c r="F37" s="11" t="n">
@@ -2746,38 +2787,38 @@
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>Frontend experience and UI/API integration</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5+ years</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Frontend Developer (React.js)</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" s="14">
         <f>IF(F38="","",CHOOSE(F38,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2792,34 +2833,34 @@
       </c>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>Core language used across backend and frontend work</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5+ years</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Frontend Developer (React.js)</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Web Application Development</t>
         </is>
       </c>
       <c r="F39" s="11" t="n">
@@ -2838,38 +2879,38 @@
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>Scalable database models and enterprise workflows</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>7.2+ years</t>
+          <t>5+ years</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>Backend Expert (Node.js)</t>
+          <t>Frontend Developer (React.js)</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" s="14">
         <f>IF(F40="","",CHOOSE(F40,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2880,11 +2921,11 @@
         <v/>
       </c>
       <c r="I40" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>Used for backend applications and API development</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2947,12 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Product Discovery</t>
         </is>
       </c>
       <c r="F41" s="11" t="n">
@@ -2930,7 +2971,7 @@
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>Database experience listed in core skills</t>
+          <t>Hands-on product discovery and requirement translation</t>
         </is>
       </c>
     </row>
@@ -2952,16 +2993,16 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Redis</t>
+          <t>PRD &amp; API Contract Writing</t>
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G42" s="14">
         <f>IF(F42="","",CHOOSE(F42,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -2972,11 +3013,11 @@
         <v/>
       </c>
       <c r="I42" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>Core skill; target deeper production-level expertise</t>
+          <t>Authors API contracts and technical documentation</t>
         </is>
       </c>
     </row>
@@ -2998,12 +3039,12 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>ORM / Data</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Sequelize</t>
+          <t>Workflow Orchestration</t>
         </is>
       </c>
       <c r="F43" s="11" t="n">
@@ -3022,7 +3063,7 @@
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>Used for Node.js backend modules</t>
+          <t>Translates complex enterprise workflows into technical flows</t>
         </is>
       </c>
     </row>
@@ -3044,16 +3085,16 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>AWS S3</t>
+          <t>Sprint Planning</t>
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G44" s="14">
         <f>IF(F44="","",CHOOSE(F44,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3068,7 +3109,7 @@
       </c>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>Cloud scalability and deployment experience</t>
+          <t>Drives sprint planning and Agile delivery</t>
         </is>
       </c>
     </row>
@@ -3090,16 +3131,16 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Grafana</t>
+          <t>Backlog Grooming</t>
         </is>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G45" s="11">
         <f>IF(F45="","",CHOOSE(F45,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3114,7 +3155,7 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>Real-time monitoring and platform stability</t>
+          <t>Experience coordinating backlog and feature velocity</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3177,12 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Stakeholder Management</t>
         </is>
       </c>
       <c r="F46" s="14" t="n">
@@ -3160,7 +3201,7 @@
       </c>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>Log analysis and proactive technical monitoring</t>
+          <t>Works with business, engineering and non-technical stakeholders</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3223,12 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>API Management</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>3scale API Management</t>
+          <t>Cross-functional Leadership</t>
         </is>
       </c>
       <c r="F47" s="11" t="n">
@@ -3206,7 +3247,7 @@
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Used for performance, maintainability and security compliance</t>
+          <t>Technical bridge between business and engineering teams</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3269,12 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>System Architecture</t>
+          <t>Team Mentoring</t>
         </is>
       </c>
       <c r="F48" s="14" t="n">
@@ -3252,7 +3293,7 @@
       </c>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>Owns architecture and technical execution roadmap</t>
+          <t>Led backend team and mentored developers</t>
         </is>
       </c>
     </row>
@@ -3274,16 +3315,16 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Node.js</t>
         </is>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G49" s="11">
         <f>IF(F49="","",CHOOSE(F49,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3298,7 +3339,7 @@
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>Focus on scalable SaaS and B2B platforms</t>
+          <t>Core backend technology across multiple roles/projects</t>
         </is>
       </c>
     </row>
@@ -3320,16 +3361,16 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Technical Debt Management</t>
+          <t>Express.js</t>
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G50" s="14">
         <f>IF(F50="","",CHOOSE(F50,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3344,7 +3385,7 @@
       </c>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>Actively manages technical debt and architectural integrity</t>
+          <t>RESTful API and backend service development</t>
         </is>
       </c>
     </row>
@@ -3366,16 +3407,16 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Framework</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Laravel Filament</t>
+          <t>RESTful APIs</t>
         </is>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G51" s="11">
         <f>IF(F51="","",CHOOSE(F51,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3386,11 +3427,11 @@
         <v/>
       </c>
       <c r="I51" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>Used for the FPNA CTRM project</t>
+          <t>Extensive API design, development and integration</t>
         </is>
       </c>
     </row>
@@ -3412,16 +3453,16 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Agile</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Agile Delivery</t>
+          <t>Microservices Architecture</t>
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G52" s="14">
         <f>IF(F52="","",CHOOSE(F52,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3436,7 +3477,7 @@
       </c>
       <c r="J52" s="13" t="inlineStr">
         <is>
-          <t>7 years of software delivery with Agile ceremonies</t>
+          <t>Designed scalable modular microservices</t>
         </is>
       </c>
     </row>
@@ -3458,16 +3499,16 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Technical Documentation</t>
+          <t>React.js</t>
         </is>
       </c>
       <c r="F53" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G53" s="11">
         <f>IF(F53="","",CHOOSE(F53,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3482,7 +3523,7 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>API contracts, technical specifications and workflow documentation</t>
+          <t>Frontend experience and UI/API integration</t>
         </is>
       </c>
     </row>
@@ -3504,16 +3545,16 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G54" s="14">
         <f>IF(F54="","",CHOOSE(F54,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3524,11 +3565,11 @@
         <v/>
       </c>
       <c r="I54" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>Common team foundation; validate level with team member</t>
+          <t>Core language used across backend and frontend work</t>
         </is>
       </c>
     </row>
@@ -3550,16 +3591,16 @@
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G55" s="11">
         <f>IF(F55="","",CHOOSE(F55,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3570,11 +3611,11 @@
         <v/>
       </c>
       <c r="I55" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>Common team foundation; validate level with team member</t>
+          <t>Scalable database models and enterprise workflows</t>
         </is>
       </c>
     </row>
@@ -3596,16 +3637,16 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" s="14">
         <f>IF(F56="","",CHOOSE(F56,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3616,11 +3657,11 @@
         <v/>
       </c>
       <c r="I56" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>Common team foundation; validate level with team member</t>
+          <t>Used for backend applications and API development</t>
         </is>
       </c>
     </row>
@@ -3642,16 +3683,16 @@
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" s="11">
         <f>IF(F57="","",CHOOSE(F57,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3662,42 +3703,42 @@
         <v/>
       </c>
       <c r="I57" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>Common team foundation; validate level with team member</t>
+          <t>Database experience listed in core skills</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>React.js</t>
+          <t>Redis</t>
         </is>
       </c>
       <c r="F58" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58" s="14">
         <f>IF(F58="","",CHOOSE(F58,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3708,38 +3749,38 @@
         <v/>
       </c>
       <c r="I58" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58" s="13" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Core skill; target deeper production-level expertise</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>ORM / Data</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Sequelize</t>
         </is>
       </c>
       <c r="F59" s="11" t="n">
@@ -3758,34 +3799,34 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Used for Node.js backend modules</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Node.js</t>
+          <t>AWS S3</t>
         </is>
       </c>
       <c r="F60" s="14" t="n">
@@ -3804,34 +3845,34 @@
       </c>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Cloud scalability and deployment experience</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Express.js</t>
+          <t>Grafana</t>
         </is>
       </c>
       <c r="F61" s="11" t="n">
@@ -3850,34 +3891,34 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Real-time monitoring and platform stability</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="F62" s="14" t="n">
@@ -3896,38 +3937,38 @@
       </c>
       <c r="J62" s="13" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Log analysis and proactive technical monitoring</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>API Management</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>3scale API Management</t>
         </is>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" s="11">
         <f>IF(F63="","",CHOOSE(F63,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -3942,34 +3983,34 @@
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Used for performance, maintainability and security compliance</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>System Architecture</t>
         </is>
       </c>
       <c r="F64" s="14" t="n">
@@ -3988,38 +4029,38 @@
       </c>
       <c r="J64" s="13" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Owns architecture and technical execution roadmap</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" s="11">
         <f>IF(F65="","",CHOOSE(F65,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4030,38 +4071,38 @@
         <v/>
       </c>
       <c r="I65" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Focus on scalable SaaS and B2B platforms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Technical Debt Management</t>
         </is>
       </c>
       <c r="F66" s="14" t="n">
@@ -4080,34 +4121,34 @@
       </c>
       <c r="J66" s="13" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Actively manages technical debt and architectural integrity</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Framework</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Laravel Filament</t>
         </is>
       </c>
       <c r="F67" s="11" t="n">
@@ -4126,38 +4167,38 @@
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Used for the FPNA CTRM project</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Agile</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>RESTful APIs</t>
+          <t>Agile Delivery</t>
         </is>
       </c>
       <c r="F68" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G68" s="14">
         <f>IF(F68="","",CHOOSE(F68,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4172,38 +4213,38 @@
       </c>
       <c r="J68" s="13" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>7 years of software delivery with Agile ceremonies</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>AI / LLM APIs</t>
+          <t>Technical Documentation</t>
         </is>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G69" s="11">
         <f>IF(F69="","",CHOOSE(F69,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4214,42 +4255,42 @@
         <v/>
       </c>
       <c r="I69" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>API contracts, technical specifications and workflow documentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="F70" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70" s="14">
         <f>IF(F70="","",CHOOSE(F70,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4260,38 +4301,38 @@
         <v/>
       </c>
       <c r="I70" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J70" s="13" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Common team foundation; validate level with team member</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>System Design</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="F71" s="11" t="n">
@@ -4310,24 +4351,24 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Common team foundation; validate level with team member</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -4337,7 +4378,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="F72" s="14" t="n">
@@ -4356,24 +4397,24 @@
       </c>
       <c r="J72" s="13" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Common team foundation; validate level with team member</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>5.5+ years</t>
+          <t>7.2+ years</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Node.js, Python)</t>
+          <t>Backend Expert (Node.js)</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -4383,7 +4424,7 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="F73" s="11" t="n">
@@ -4402,7 +4443,7 @@
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Common team foundation; validate level with team member</t>
         </is>
       </c>
     </row>
@@ -4424,16 +4465,16 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>React.js</t>
         </is>
       </c>
       <c r="F74" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" s="14">
         <f>IF(F74="","",CHOOSE(F74,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4444,7 +4485,7 @@
         <v/>
       </c>
       <c r="I74" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J74" s="13" t="inlineStr">
         <is>
@@ -4455,17 +4496,17 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -4475,7 +4516,7 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>React.js</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="F75" s="11" t="n">
@@ -4501,27 +4542,27 @@
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Node.js</t>
         </is>
       </c>
       <c r="F76" s="14" t="n">
@@ -4547,17 +4588,17 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -4567,7 +4608,7 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Node.js</t>
+          <t>Express.js</t>
         </is>
       </c>
       <c r="F77" s="11" t="n">
@@ -4593,31 +4634,31 @@
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Express.js</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="F78" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" s="14">
         <f>IF(F78="","",CHOOSE(F78,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4628,7 +4669,7 @@
         <v/>
       </c>
       <c r="I78" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J78" s="13" t="inlineStr">
         <is>
@@ -4639,17 +4680,17 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -4659,11 +4700,11 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="F79" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G79" s="11">
         <f>IF(F79="","",CHOOSE(F79,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4685,17 +4726,17 @@
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -4705,11 +4746,11 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="F80" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" s="14">
         <f>IF(F80="","",CHOOSE(F80,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4720,7 +4761,7 @@
         <v/>
       </c>
       <c r="I80" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J80" s="13" t="inlineStr">
         <is>
@@ -4731,27 +4772,27 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="F81" s="11" t="n">
@@ -4777,17 +4818,17 @@
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -4801,7 +4842,7 @@
         </is>
       </c>
       <c r="F82" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" s="14">
         <f>IF(F82="","",CHOOSE(F82,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4812,7 +4853,7 @@
         <v/>
       </c>
       <c r="I82" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" s="13" t="inlineStr">
         <is>
@@ -4823,31 +4864,31 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>AI / Automation</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>AI Web Scraping</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="F83" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G83" s="11">
         <f>IF(F83="","",CHOOSE(F83,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4858,7 +4899,7 @@
         <v/>
       </c>
       <c r="I83" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
@@ -4869,27 +4910,27 @@
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>AI / Automation</t>
+          <t>API</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Web Scraping</t>
+          <t>RESTful APIs</t>
         </is>
       </c>
       <c r="F84" s="14" t="n">
@@ -4915,27 +4956,27 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>RESTful APIs</t>
+          <t>AI / LLM APIs</t>
         </is>
       </c>
       <c r="F85" s="11" t="n">
@@ -4961,31 +5002,31 @@
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="F86" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G86" s="14">
         <f>IF(F86="","",CHOOSE(F86,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -4996,7 +5037,7 @@
         <v/>
       </c>
       <c r="I86" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J86" s="13" t="inlineStr">
         <is>
@@ -5007,31 +5048,31 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="F87" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" s="11">
         <f>IF(F87="","",CHOOSE(F87,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5042,7 +5083,7 @@
         <v/>
       </c>
       <c r="I87" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
@@ -5053,27 +5094,27 @@
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>System Design</t>
         </is>
       </c>
       <c r="F88" s="14" t="n">
@@ -5099,17 +5140,17 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -5119,7 +5160,7 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="F89" s="11" t="n">
@@ -5145,27 +5186,27 @@
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="F90" s="14" t="n">
@@ -5191,27 +5232,27 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>5.5+ years</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Node.js, Python)</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>React.js</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="F91" s="11" t="n">
@@ -5237,31 +5278,31 @@
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>React.js</t>
         </is>
       </c>
       <c r="F92" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" s="14">
         <f>IF(F92="","",CHOOSE(F92,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5272,7 +5313,7 @@
         <v/>
       </c>
       <c r="I92" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J92" s="13" t="inlineStr">
         <is>
@@ -5283,31 +5324,31 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="F93" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" s="11">
         <f>IF(F93="","",CHOOSE(F93,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5318,7 +5359,7 @@
         <v/>
       </c>
       <c r="I93" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
@@ -5329,17 +5370,17 @@
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -5353,7 +5394,7 @@
         </is>
       </c>
       <c r="F94" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" s="14">
         <f>IF(F94="","",CHOOSE(F94,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5364,7 +5405,7 @@
         <v/>
       </c>
       <c r="I94" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J94" s="13" t="inlineStr">
         <is>
@@ -5375,17 +5416,17 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -5399,7 +5440,7 @@
         </is>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G95" s="11">
         <f>IF(F95="","",CHOOSE(F95,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5421,31 +5462,31 @@
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="F96" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G96" s="14">
         <f>IF(F96="","",CHOOSE(F96,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5456,7 +5497,7 @@
         <v/>
       </c>
       <c r="I96" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J96" s="13" t="inlineStr">
         <is>
@@ -5467,31 +5508,31 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G97" s="11">
         <f>IF(F97="","",CHOOSE(F97,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5513,27 +5554,27 @@
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>RESTful APIs</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="F98" s="14" t="n">
@@ -5559,27 +5600,27 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="F99" s="11" t="n">
@@ -5605,31 +5646,31 @@
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>AI / Automation</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>AI Web Scraping</t>
         </is>
       </c>
       <c r="F100" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" s="14">
         <f>IF(F100="","",CHOOSE(F100,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5640,7 +5681,7 @@
         <v/>
       </c>
       <c r="I100" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J100" s="13" t="inlineStr">
         <is>
@@ -5651,31 +5692,31 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>AI / Automation</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Web Scraping</t>
         </is>
       </c>
       <c r="F101" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" s="11">
         <f>IF(F101="","",CHOOSE(F101,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5686,7 +5727,7 @@
         <v/>
       </c>
       <c r="I101" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
@@ -5697,27 +5738,27 @@
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>API</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>RESTful APIs</t>
         </is>
       </c>
       <c r="F102" s="14" t="n">
@@ -5743,31 +5784,31 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Next.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="F103" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G103" s="11">
         <f>IF(F103="","",CHOOSE(F103,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5778,7 +5819,7 @@
         <v/>
       </c>
       <c r="I103" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
@@ -5789,31 +5830,31 @@
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="F104" s="14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G104" s="14">
         <f>IF(F104="","",CHOOSE(F104,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5824,42 +5865,42 @@
         <v/>
       </c>
       <c r="I104" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J104" s="13" t="inlineStr">
         <is>
-          <t>Primary skill</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="F105" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G105" s="11">
         <f>IF(F105="","",CHOOSE(F105,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5870,38 +5911,42 @@
         <v/>
       </c>
       <c r="I105" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J105" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J105" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>4+ years</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (React, Next.js, Node.js, AI Web Scraping)</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="F106" s="14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G106" s="14">
         <f>IF(F106="","",CHOOSE(F106,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5912,24 +5957,28 @@
         <v/>
       </c>
       <c r="I106" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J106" s="13" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J106" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
@@ -5939,11 +5988,11 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>HTML5</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="F107" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G107" s="11">
         <f>IF(F107="","",CHOOSE(F107,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5954,24 +6003,28 @@
         <v/>
       </c>
       <c r="I107" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J107" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J107" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -5981,11 +6034,11 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>CSS / SCSS</t>
+          <t>React.js</t>
         </is>
       </c>
       <c r="F108" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G108" s="14">
         <f>IF(F108="","",CHOOSE(F108,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -5996,38 +6049,42 @@
         <v/>
       </c>
       <c r="I108" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J108" s="13" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J108" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>RxJS</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="F109" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G109" s="11">
         <f>IF(F109="","",CHOOSE(F109,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6038,34 +6095,38 @@
         <v/>
       </c>
       <c r="I109" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J109" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J109" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>NgRx</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="F110" s="14" t="n">
@@ -6080,42 +6141,42 @@
         <v/>
       </c>
       <c r="I110" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J110" s="13" t="inlineStr">
         <is>
-          <t>Improve advanced state management</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>Angular Material</t>
+          <t>Node.js</t>
         </is>
       </c>
       <c r="F111" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G111" s="11">
         <f>IF(F111="","",CHOOSE(F111,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6128,36 +6189,40 @@
       <c r="I111" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="J111" s="10" t="inlineStr"/>
+      <c r="J111" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>PrimeNG</t>
+          <t>Express.js</t>
         </is>
       </c>
       <c r="F112" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G112" s="14">
         <f>IF(F112="","",CHOOSE(F112,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6170,36 +6235,40 @@
       <c r="I112" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="J112" s="13" t="inlineStr"/>
+      <c r="J112" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>Micro Frontend</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="F113" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G113" s="11">
         <f>IF(F113="","",CHOOSE(F113,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6210,38 +6279,42 @@
         <v/>
       </c>
       <c r="I113" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J113" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J113" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>Module Federation</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="F114" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G114" s="14">
         <f>IF(F114="","",CHOOSE(F114,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6252,24 +6325,28 @@
         <v/>
       </c>
       <c r="I114" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J114" s="13" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J114" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -6279,11 +6356,11 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>REST APIs</t>
+          <t>RESTful APIs</t>
         </is>
       </c>
       <c r="F115" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G115" s="11">
         <f>IF(F115="","",CHOOSE(F115,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6294,38 +6371,42 @@
         <v/>
       </c>
       <c r="I115" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J115" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J115" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="F116" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G116" s="14">
         <f>IF(F116="","",CHOOSE(F116,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6336,38 +6417,42 @@
         <v/>
       </c>
       <c r="I116" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J116" s="13" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J116" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>Node.js</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="F117" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G117" s="11">
         <f>IF(F117="","",CHOOSE(F117,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6382,38 +6467,38 @@
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>Currently learning</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>Express.js</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="F118" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G118" s="14">
         <f>IF(F118="","",CHOOSE(F118,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6426,36 +6511,40 @@
       <c r="I118" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="J118" s="13" t="inlineStr"/>
+      <c r="J118" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="F119" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G119" s="11">
         <f>IF(F119="","",CHOOSE(F119,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6468,32 +6557,36 @@
       <c r="I119" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="J119" s="10" t="inlineStr"/>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>System Design</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="F120" s="14" t="n">
@@ -6510,36 +6603,40 @@
       <c r="I120" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="J120" s="13" t="inlineStr"/>
+      <c r="J120" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>6+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer (Angular, Node.js)</t>
+          <t>Full Stack Developer (Next.js)</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>AWS / Cloud</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G121" s="11">
         <f>IF(F121="","",CHOOSE(F121,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6550,11 +6647,11 @@
         <v/>
       </c>
       <c r="I121" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>Build practical cloud knowledge</t>
+          <t>Role-based starter rating; validate with team member</t>
         </is>
       </c>
     </row>
@@ -6576,16 +6673,16 @@
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>CI/CD</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="F122" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G122" s="14">
         <f>IF(F122="","",CHOOSE(F122,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6596,9 +6693,13 @@
         <v/>
       </c>
       <c r="I122" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J122" s="13" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J122" s="13" t="inlineStr">
+        <is>
+          <t>Primary skill</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
@@ -6618,16 +6719,16 @@
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G123" s="11">
         <f>IF(F123="","",CHOOSE(F123,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6638,7 +6739,7 @@
         <v/>
       </c>
       <c r="I123" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J123" s="10" t="inlineStr"/>
     </row>
@@ -6660,16 +6761,16 @@
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
         <is>
-          <t>AI / LLM APIs</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="F124" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G124" s="14">
         <f>IF(F124="","",CHOOSE(F124,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6680,7 +6781,7 @@
         <v/>
       </c>
       <c r="I124" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J124" s="13" t="inlineStr"/>
     </row>
@@ -6702,16 +6803,16 @@
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>Agentic AI</t>
+          <t>HTML5</t>
         </is>
       </c>
       <c r="F125" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G125" s="11">
         <f>IF(F125="","",CHOOSE(F125,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6722,7 +6823,7 @@
         <v/>
       </c>
       <c r="I125" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J125" s="10" t="inlineStr"/>
     </row>
@@ -6744,16 +6845,16 @@
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>CSS / SCSS</t>
         </is>
       </c>
       <c r="F126" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G126" s="14">
         <f>IF(F126="","",CHOOSE(F126,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6764,13 +6865,9 @@
         <v/>
       </c>
       <c r="I126" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J126" s="13" t="inlineStr">
-        <is>
-          <t>Common team foundation; validate level with team member</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J126" s="13" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
@@ -6790,16 +6887,16 @@
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>RxJS</t>
         </is>
       </c>
       <c r="F127" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G127" s="11">
         <f>IF(F127="","",CHOOSE(F127,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6810,13 +6907,9 @@
         <v/>
       </c>
       <c r="I127" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J127" s="10" t="inlineStr">
-        <is>
-          <t>Common team foundation; validate level with team member</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J127" s="10" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
@@ -6836,12 +6929,12 @@
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>NgRx</t>
         </is>
       </c>
       <c r="F128" s="14" t="n">
@@ -6856,18 +6949,18 @@
         <v/>
       </c>
       <c r="I128" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J128" s="13" t="inlineStr">
         <is>
-          <t>Common team foundation; validate level with team member</t>
+          <t>Improve advanced state management</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -6877,21 +6970,21 @@
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>ServiceNow ITAM</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>SAM Pro</t>
+          <t>Angular Material</t>
         </is>
       </c>
       <c r="F129" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G129" s="11">
         <f>IF(F129="","",CHOOSE(F129,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -6902,18 +6995,14 @@
         <v/>
       </c>
       <c r="I129" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J129" s="10" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B130" s="12" t="inlineStr">
@@ -6923,17 +7012,17 @@
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>ServiceNow ITAM</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>AICT</t>
+          <t>PrimeNG</t>
         </is>
       </c>
       <c r="F130" s="14" t="n">
@@ -6948,18 +7037,14 @@
         <v/>
       </c>
       <c r="I130" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J130" s="13" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J130" s="13" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -6969,17 +7054,17 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>ServiceNow ITAM</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>Asset Lifecycle Management</t>
+          <t>Micro Frontend</t>
         </is>
       </c>
       <c r="F131" s="11" t="n">
@@ -6996,16 +7081,12 @@
       <c r="I131" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="J131" s="10" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+      <c r="J131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B132" s="12" t="inlineStr">
@@ -7015,17 +7096,17 @@
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>SAM Implementation</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>Implementation &amp; Migration</t>
+          <t>Module Federation</t>
         </is>
       </c>
       <c r="F132" s="14" t="n">
@@ -7042,16 +7123,12 @@
       <c r="I132" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="J132" s="13" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+      <c r="J132" s="13" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -7061,21 +7138,21 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>API</t>
         </is>
       </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
-          <t>License Management</t>
+          <t>REST APIs</t>
         </is>
       </c>
       <c r="F133" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G133" s="11">
         <f>IF(F133="","",CHOOSE(F133,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7088,16 +7165,12 @@
       <c r="I133" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="J133" s="10" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+      <c r="J133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B134" s="12" t="inlineStr">
@@ -7107,17 +7180,17 @@
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>License Optimization</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="F134" s="14" t="n">
@@ -7134,16 +7207,12 @@
       <c r="I134" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="J134" s="13" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+      <c r="J134" s="13" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -7153,21 +7222,21 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
-          <t>Software Compliance</t>
+          <t>Node.js</t>
         </is>
       </c>
       <c r="F135" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G135" s="11">
         <f>IF(F135="","",CHOOSE(F135,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7178,18 +7247,18 @@
         <v/>
       </c>
       <c r="I135" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Currently learning</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B136" s="12" t="inlineStr">
@@ -7199,21 +7268,21 @@
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>Licensing</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>Microsoft Licensing</t>
+          <t>Express.js</t>
         </is>
       </c>
       <c r="F136" s="14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G136" s="14">
         <f>IF(F136="","",CHOOSE(F136,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7224,18 +7293,14 @@
         <v/>
       </c>
       <c r="I136" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J136" s="13" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J136" s="13" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -7245,21 +7310,21 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>Licensing</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>Adobe Licensing</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="F137" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G137" s="11">
         <f>IF(F137="","",CHOOSE(F137,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7270,18 +7335,14 @@
         <v/>
       </c>
       <c r="I137" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J137" s="10" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J137" s="10" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B138" s="12" t="inlineStr">
@@ -7291,21 +7352,21 @@
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>Licensing</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>Atlassian / Oracle Licensing</t>
+          <t>System Design</t>
         </is>
       </c>
       <c r="F138" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G138" s="14">
         <f>IF(F138="","",CHOOSE(F138,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7316,18 +7377,14 @@
         <v/>
       </c>
       <c r="I138" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J138" s="13" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J138" s="13" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -7337,21 +7394,21 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>Licensing</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>SaaS / FOSS Assessment</t>
+          <t>AWS / Cloud</t>
         </is>
       </c>
       <c r="F139" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G139" s="11">
         <f>IF(F139="","",CHOOSE(F139,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7362,18 +7419,18 @@
         <v/>
       </c>
       <c r="I139" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J139" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Build practical cloud knowledge</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B140" s="12" t="inlineStr">
@@ -7383,21 +7440,21 @@
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>Discovery &amp; Inventory</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
         <is>
-          <t>SCCM / Intune</t>
+          <t>CI/CD</t>
         </is>
       </c>
       <c r="F140" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G140" s="14">
         <f>IF(F140="","",CHOOSE(F140,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7408,18 +7465,14 @@
         <v/>
       </c>
       <c r="I140" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J140" s="13" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J140" s="13" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -7429,21 +7482,21 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>Discovery &amp; Inventory</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>Jamf / Defender / InfraSecure</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="F141" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G141" s="11">
         <f>IF(F141="","",CHOOSE(F141,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7454,18 +7507,14 @@
         <v/>
       </c>
       <c r="I141" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J141" s="10" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J141" s="10" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B142" s="12" t="inlineStr">
@@ -7475,21 +7524,21 @@
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>ServiceNow Platform</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>Administration &amp; Configuration</t>
+          <t>AI / LLM APIs</t>
         </is>
       </c>
       <c r="F142" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G142" s="14">
         <f>IF(F142="","",CHOOSE(F142,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7500,18 +7549,14 @@
         <v/>
       </c>
       <c r="I142" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J142" s="13" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J142" s="13" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -7521,21 +7566,21 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>Stakeholder Management</t>
+          <t>Agentic AI</t>
         </is>
       </c>
       <c r="F143" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G143" s="11">
         <f>IF(F143="","",CHOOSE(F143,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7546,18 +7591,14 @@
         <v/>
       </c>
       <c r="I143" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J143" s="10" t="inlineStr">
-        <is>
-          <t>Role-based starter rating; validate with team member</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J143" s="10" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B144" s="12" t="inlineStr">
@@ -7567,21 +7608,21 @@
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E144" s="12" t="inlineStr">
         <is>
-          <t>UAT / Process / Go-Live</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="F144" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G144" s="14">
         <f>IF(F144="","",CHOOSE(F144,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7592,18 +7633,18 @@
         <v/>
       </c>
       <c r="I144" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J144" s="13" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Common team foundation; validate level with team member</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -7613,21 +7654,21 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>Dashboards &amp; Reporting</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="F145" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G145" s="11">
         <f>IF(F145="","",CHOOSE(F145,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7638,42 +7679,42 @@
         <v/>
       </c>
       <c r="I145" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J145" s="10" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Common team foundation; validate level with team member</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>Full Stack Software Developer (Angular, Node.js)</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr">
         <is>
-          <t>Project Planning</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="F146" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G146" s="14">
         <f>IF(F146="","",CHOOSE(F146,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7684,42 +7725,42 @@
         <v/>
       </c>
       <c r="I146" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J146" s="13" t="inlineStr">
         <is>
-          <t>Role-based starter rating; validate with team member</t>
+          <t>Common team foundation; validate level with team member</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>ServiceNow ITAM</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>Sprint Planning</t>
+          <t>SAM Pro</t>
         </is>
       </c>
       <c r="F147" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G147" s="11">
         <f>IF(F147="","",CHOOSE(F147,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7741,31 +7782,31 @@
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>ServiceNow ITAM</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
         <is>
-          <t>Backlog Grooming</t>
+          <t>AICT</t>
         </is>
       </c>
       <c r="F148" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G148" s="14">
         <f>IF(F148="","",CHOOSE(F148,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7776,7 +7817,7 @@
         <v/>
       </c>
       <c r="I148" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J148" s="13" t="inlineStr">
         <is>
@@ -7787,27 +7828,27 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>ServiceNow ITAM</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Asset Lifecycle Management</t>
         </is>
       </c>
       <c r="F149" s="11" t="n">
@@ -7833,27 +7874,27 @@
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>SAM Implementation</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>Stakeholder Management</t>
+          <t>Implementation &amp; Migration</t>
         </is>
       </c>
       <c r="F150" s="14" t="n">
@@ -7879,31 +7920,31 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>Team Coordination</t>
+          <t>License Management</t>
         </is>
       </c>
       <c r="F151" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G151" s="11">
         <f>IF(F151="","",CHOOSE(F151,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7925,31 +7966,31 @@
     <row r="152">
       <c r="A152" s="12" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C152" s="13" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>Agile</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
-          <t>Agile Delivery</t>
+          <t>License Optimization</t>
         </is>
       </c>
       <c r="F152" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G152" s="14">
         <f>IF(F152="","",CHOOSE(F152,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -7960,7 +8001,7 @@
         <v/>
       </c>
       <c r="I152" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J152" s="13" t="inlineStr">
         <is>
@@ -7971,27 +8012,27 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>Digital Marketing</t>
+          <t>Software Compliance</t>
         </is>
       </c>
       <c r="F153" s="11" t="n">
@@ -8017,31 +8058,31 @@
     <row r="154">
       <c r="A154" s="12" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C154" s="13" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Licensing</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
         <is>
-          <t>Content Strategy</t>
+          <t>Microsoft Licensing</t>
         </is>
       </c>
       <c r="F154" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G154" s="14">
         <f>IF(F154="","",CHOOSE(F154,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -8063,31 +8104,31 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Licensing</t>
         </is>
       </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Adobe Licensing</t>
         </is>
       </c>
       <c r="F155" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G155" s="11">
         <f>IF(F155="","",CHOOSE(F155,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -8109,27 +8150,27 @@
     <row r="156">
       <c r="A156" s="12" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C156" s="13" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Licensing</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
         <is>
-          <t>Social Media Marketing</t>
+          <t>Atlassian / Oracle Licensing</t>
         </is>
       </c>
       <c r="F156" s="14" t="n">
@@ -8155,31 +8196,31 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Licensing</t>
         </is>
       </c>
       <c r="E157" s="9" t="inlineStr">
         <is>
-          <t>Marketing Analytics</t>
+          <t>SaaS / FOSS Assessment</t>
         </is>
       </c>
       <c r="F157" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G157" s="11">
         <f>IF(F157="","",CHOOSE(F157,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -8190,7 +8231,7 @@
         <v/>
       </c>
       <c r="I157" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J157" s="10" t="inlineStr">
         <is>
@@ -8201,27 +8242,27 @@
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C158" s="13" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Discovery &amp; Inventory</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
         <is>
-          <t>Presentation Skills</t>
+          <t>SCCM / Intune</t>
         </is>
       </c>
       <c r="F158" s="14" t="n">
@@ -8247,31 +8288,31 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Discovery &amp; Inventory</t>
         </is>
       </c>
       <c r="E159" s="9" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Jamf / Defender / InfraSecure</t>
         </is>
       </c>
       <c r="F159" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G159" s="11">
         <f>IF(F159="","",CHOOSE(F159,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -8282,7 +8323,7 @@
         <v/>
       </c>
       <c r="I159" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J159" s="10" t="inlineStr">
         <is>
@@ -8293,31 +8334,31 @@
     <row r="160">
       <c r="A160" s="12" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>ServiceNow Platform</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Administration &amp; Configuration</t>
         </is>
       </c>
       <c r="F160" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G160" s="14">
         <f>IF(F160="","",CHOOSE(F160,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -8328,7 +8369,7 @@
         <v/>
       </c>
       <c r="I160" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J160" s="13" t="inlineStr">
         <is>
@@ -8339,31 +8380,31 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>Stakeholder Management</t>
         </is>
       </c>
       <c r="F161" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G161" s="11">
         <f>IF(F161="","",CHOOSE(F161,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -8374,7 +8415,7 @@
         <v/>
       </c>
       <c r="I161" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J161" s="10" t="inlineStr">
         <is>
@@ -8385,31 +8426,31 @@
     <row r="162">
       <c r="A162" s="12" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>UAT / Process / Go-Live</t>
         </is>
       </c>
       <c r="F162" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G162" s="14">
         <f>IF(F162="","",CHOOSE(F162,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -8420,7 +8461,7 @@
         <v/>
       </c>
       <c r="I162" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J162" s="13" t="inlineStr">
         <is>
@@ -8431,31 +8472,31 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>Swhetha Talreja</t>
+          <t>Suraj Sharma</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>4+ years</t>
+          <t>6+ years</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Project Management and Digital Marketing Expert</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="E163" s="9" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Dashboards &amp; Reporting</t>
         </is>
       </c>
       <c r="F163" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G163" s="11">
         <f>IF(F163="","",CHOOSE(F163,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
@@ -8466,7 +8507,7 @@
         <v/>
       </c>
       <c r="I163" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J163" s="10" t="inlineStr">
         <is>
@@ -8475,12 +8516,34 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="12" t="n"/>
-      <c r="B164" s="12" t="n"/>
-      <c r="C164" s="13" t="n"/>
-      <c r="D164" s="12" t="n"/>
-      <c r="E164" s="12" t="n"/>
-      <c r="F164" s="14" t="n"/>
+      <c r="A164" s="12" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B164" s="12" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C164" s="13" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>Project Planning</t>
+        </is>
+      </c>
+      <c r="F164" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="G164" s="14">
         <f>IF(F164="","",CHOOSE(F164,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8489,16 +8552,44 @@
         <f>IF(F164="","",IF(I164="","Set target",IF(F164&gt;=I164,"Strong",IF(F164=I164-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I164" s="14" t="n"/>
-      <c r="J164" s="13" t="n"/>
+      <c r="I164" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J164" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="9" t="n"/>
-      <c r="B165" s="9" t="n"/>
-      <c r="C165" s="10" t="n"/>
-      <c r="D165" s="9" t="n"/>
-      <c r="E165" s="9" t="n"/>
-      <c r="F165" s="11" t="n"/>
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
+      <c r="E165" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Planning</t>
+        </is>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="G165" s="11">
         <f>IF(F165="","",CHOOSE(F165,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8507,16 +8598,44 @@
         <f>IF(F165="","",IF(I165="","Set target",IF(F165&gt;=I165,"Strong",IF(F165=I165-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I165" s="11" t="n"/>
-      <c r="J165" s="10" t="n"/>
+      <c r="I165" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J165" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="12" t="n"/>
-      <c r="B166" s="12" t="n"/>
-      <c r="C166" s="13" t="n"/>
-      <c r="D166" s="12" t="n"/>
-      <c r="E166" s="12" t="n"/>
-      <c r="F166" s="14" t="n"/>
+      <c r="A166" s="12" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C166" s="13" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr">
+        <is>
+          <t>Backlog Grooming</t>
+        </is>
+      </c>
+      <c r="F166" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="G166" s="14">
         <f>IF(F166="","",CHOOSE(F166,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8525,16 +8644,44 @@
         <f>IF(F166="","",IF(I166="","Set target",IF(F166&gt;=I166,"Strong",IF(F166=I166-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I166" s="14" t="n"/>
-      <c r="J166" s="13" t="n"/>
+      <c r="I166" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J166" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="n"/>
-      <c r="B167" s="9" t="n"/>
-      <c r="C167" s="10" t="n"/>
-      <c r="D167" s="9" t="n"/>
-      <c r="E167" s="9" t="n"/>
-      <c r="F167" s="11" t="n"/>
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B167" s="9" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
+      <c r="E167" s="9" t="inlineStr">
+        <is>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="G167" s="11">
         <f>IF(F167="","",CHOOSE(F167,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8543,16 +8690,44 @@
         <f>IF(F167="","",IF(I167="","Set target",IF(F167&gt;=I167,"Strong",IF(F167=I167-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I167" s="11" t="n"/>
-      <c r="J167" s="10" t="n"/>
+      <c r="I167" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J167" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="12" t="n"/>
-      <c r="B168" s="12" t="n"/>
-      <c r="C168" s="13" t="n"/>
-      <c r="D168" s="12" t="n"/>
-      <c r="E168" s="12" t="n"/>
-      <c r="F168" s="14" t="n"/>
+      <c r="A168" s="12" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B168" s="12" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C168" s="13" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D168" s="12" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E168" s="12" t="inlineStr">
+        <is>
+          <t>Stakeholder Management</t>
+        </is>
+      </c>
+      <c r="F168" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="G168" s="14">
         <f>IF(F168="","",CHOOSE(F168,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8561,16 +8736,44 @@
         <f>IF(F168="","",IF(I168="","Set target",IF(F168&gt;=I168,"Strong",IF(F168=I168-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I168" s="14" t="n"/>
-      <c r="J168" s="13" t="n"/>
+      <c r="I168" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J168" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="n"/>
-      <c r="B169" s="9" t="n"/>
-      <c r="C169" s="10" t="n"/>
-      <c r="D169" s="9" t="n"/>
-      <c r="E169" s="9" t="n"/>
-      <c r="F169" s="11" t="n"/>
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E169" s="9" t="inlineStr">
+        <is>
+          <t>Team Coordination</t>
+        </is>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="G169" s="11">
         <f>IF(F169="","",CHOOSE(F169,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8579,16 +8782,44 @@
         <f>IF(F169="","",IF(I169="","Set target",IF(F169&gt;=I169,"Strong",IF(F169=I169-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I169" s="11" t="n"/>
-      <c r="J169" s="10" t="n"/>
+      <c r="I169" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J169" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="12" t="n"/>
-      <c r="B170" s="12" t="n"/>
-      <c r="C170" s="13" t="n"/>
-      <c r="D170" s="12" t="n"/>
-      <c r="E170" s="12" t="n"/>
-      <c r="F170" s="14" t="n"/>
+      <c r="A170" s="12" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C170" s="13" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D170" s="12" t="inlineStr">
+        <is>
+          <t>Agile</t>
+        </is>
+      </c>
+      <c r="E170" s="12" t="inlineStr">
+        <is>
+          <t>Agile Delivery</t>
+        </is>
+      </c>
+      <c r="F170" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="G170" s="14">
         <f>IF(F170="","",CHOOSE(F170,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8597,16 +8828,44 @@
         <f>IF(F170="","",IF(I170="","Set target",IF(F170&gt;=I170,"Strong",IF(F170=I170-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I170" s="14" t="n"/>
-      <c r="J170" s="13" t="n"/>
+      <c r="I170" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J170" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="9" t="n"/>
-      <c r="B171" s="9" t="n"/>
-      <c r="C171" s="10" t="n"/>
-      <c r="D171" s="9" t="n"/>
-      <c r="E171" s="9" t="n"/>
-      <c r="F171" s="11" t="n"/>
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
+          <t>Digital Marketing</t>
+        </is>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="G171" s="11">
         <f>IF(F171="","",CHOOSE(F171,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8615,16 +8874,44 @@
         <f>IF(F171="","",IF(I171="","Set target",IF(F171&gt;=I171,"Strong",IF(F171=I171-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I171" s="11" t="n"/>
-      <c r="J171" s="10" t="n"/>
+      <c r="I171" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J171" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="12" t="n"/>
-      <c r="B172" s="12" t="n"/>
-      <c r="C172" s="13" t="n"/>
-      <c r="D172" s="12" t="n"/>
-      <c r="E172" s="12" t="n"/>
-      <c r="F172" s="14" t="n"/>
+      <c r="A172" s="12" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B172" s="12" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C172" s="13" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D172" s="12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E172" s="12" t="inlineStr">
+        <is>
+          <t>Content Strategy</t>
+        </is>
+      </c>
+      <c r="F172" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="G172" s="14">
         <f>IF(F172="","",CHOOSE(F172,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8633,16 +8920,44 @@
         <f>IF(F172="","",IF(I172="","Set target",IF(F172&gt;=I172,"Strong",IF(F172=I172-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I172" s="14" t="n"/>
-      <c r="J172" s="13" t="n"/>
+      <c r="I172" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J172" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="9" t="n"/>
-      <c r="B173" s="9" t="n"/>
-      <c r="C173" s="10" t="n"/>
-      <c r="D173" s="9" t="n"/>
-      <c r="E173" s="9" t="n"/>
-      <c r="F173" s="11" t="n"/>
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E173" s="9" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="G173" s="11">
         <f>IF(F173="","",CHOOSE(F173,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8651,16 +8966,44 @@
         <f>IF(F173="","",IF(I173="","Set target",IF(F173&gt;=I173,"Strong",IF(F173=I173-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I173" s="11" t="n"/>
-      <c r="J173" s="10" t="n"/>
+      <c r="I173" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J173" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="12" t="n"/>
-      <c r="B174" s="12" t="n"/>
-      <c r="C174" s="13" t="n"/>
-      <c r="D174" s="12" t="n"/>
-      <c r="E174" s="12" t="n"/>
-      <c r="F174" s="14" t="n"/>
+      <c r="A174" s="12" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C174" s="13" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="inlineStr">
+        <is>
+          <t>Social Media Marketing</t>
+        </is>
+      </c>
+      <c r="F174" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="G174" s="14">
         <f>IF(F174="","",CHOOSE(F174,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8669,16 +9012,44 @@
         <f>IF(F174="","",IF(I174="","Set target",IF(F174&gt;=I174,"Strong",IF(F174=I174-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I174" s="14" t="n"/>
-      <c r="J174" s="13" t="n"/>
+      <c r="I174" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J174" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="9" t="n"/>
-      <c r="B175" s="9" t="n"/>
-      <c r="C175" s="10" t="n"/>
-      <c r="D175" s="9" t="n"/>
-      <c r="E175" s="9" t="n"/>
-      <c r="F175" s="11" t="n"/>
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C175" s="10" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="E175" s="9" t="inlineStr">
+        <is>
+          <t>Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="G175" s="11">
         <f>IF(F175="","",CHOOSE(F175,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8687,16 +9058,44 @@
         <f>IF(F175="","",IF(I175="","Set target",IF(F175&gt;=I175,"Strong",IF(F175=I175-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I175" s="11" t="n"/>
-      <c r="J175" s="10" t="n"/>
+      <c r="I175" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J175" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="12" t="n"/>
-      <c r="B176" s="12" t="n"/>
-      <c r="C176" s="13" t="n"/>
-      <c r="D176" s="12" t="n"/>
-      <c r="E176" s="12" t="n"/>
-      <c r="F176" s="14" t="n"/>
+      <c r="A176" s="12" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B176" s="12" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C176" s="13" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D176" s="12" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="E176" s="12" t="inlineStr">
+        <is>
+          <t>Presentation Skills</t>
+        </is>
+      </c>
+      <c r="F176" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="G176" s="14">
         <f>IF(F176="","",CHOOSE(F176,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8705,16 +9104,44 @@
         <f>IF(F176="","",IF(I176="","Set target",IF(F176&gt;=I176,"Strong",IF(F176=I176-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I176" s="14" t="n"/>
-      <c r="J176" s="13" t="n"/>
+      <c r="I176" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J176" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="9" t="n"/>
-      <c r="B177" s="9" t="n"/>
-      <c r="C177" s="10" t="n"/>
-      <c r="D177" s="9" t="n"/>
-      <c r="E177" s="9" t="n"/>
-      <c r="F177" s="11" t="n"/>
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C177" s="10" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>Common Foundation</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="G177" s="11">
         <f>IF(F177="","",CHOOSE(F177,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8723,16 +9150,44 @@
         <f>IF(F177="","",IF(I177="","Set target",IF(F177&gt;=I177,"Strong",IF(F177=I177-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I177" s="11" t="n"/>
-      <c r="J177" s="10" t="n"/>
+      <c r="I177" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J177" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="12" t="n"/>
-      <c r="B178" s="12" t="n"/>
-      <c r="C178" s="13" t="n"/>
-      <c r="D178" s="12" t="n"/>
-      <c r="E178" s="12" t="n"/>
-      <c r="F178" s="14" t="n"/>
+      <c r="A178" s="12" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B178" s="12" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C178" s="13" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
+        <is>
+          <t>Common Foundation</t>
+        </is>
+      </c>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="F178" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="G178" s="14">
         <f>IF(F178="","",CHOOSE(F178,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8741,16 +9196,44 @@
         <f>IF(F178="","",IF(I178="","Set target",IF(F178&gt;=I178,"Strong",IF(F178=I178-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I178" s="14" t="n"/>
-      <c r="J178" s="13" t="n"/>
+      <c r="I178" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J178" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="9" t="n"/>
-      <c r="B179" s="9" t="n"/>
-      <c r="C179" s="10" t="n"/>
-      <c r="D179" s="9" t="n"/>
-      <c r="E179" s="9" t="n"/>
-      <c r="F179" s="11" t="n"/>
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>Common Foundation</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="G179" s="11">
         <f>IF(F179="","",CHOOSE(F179,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8759,16 +9242,44 @@
         <f>IF(F179="","",IF(I179="","Set target",IF(F179&gt;=I179,"Strong",IF(F179=I179-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I179" s="11" t="n"/>
-      <c r="J179" s="10" t="n"/>
+      <c r="I179" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J179" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="12" t="n"/>
-      <c r="B180" s="12" t="n"/>
-      <c r="C180" s="13" t="n"/>
-      <c r="D180" s="12" t="n"/>
-      <c r="E180" s="12" t="n"/>
-      <c r="F180" s="14" t="n"/>
+      <c r="A180" s="12" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B180" s="12" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C180" s="13" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D180" s="12" t="inlineStr">
+        <is>
+          <t>Common Foundation</t>
+        </is>
+      </c>
+      <c r="E180" s="12" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="F180" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="G180" s="14">
         <f>IF(F180="","",CHOOSE(F180,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8777,16 +9288,44 @@
         <f>IF(F180="","",IF(I180="","Set target",IF(F180&gt;=I180,"Strong",IF(F180=I180-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I180" s="14" t="n"/>
-      <c r="J180" s="13" t="n"/>
+      <c r="I180" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J180" s="13" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="9" t="n"/>
-      <c r="B181" s="9" t="n"/>
-      <c r="C181" s="10" t="n"/>
-      <c r="D181" s="9" t="n"/>
-      <c r="E181" s="9" t="n"/>
-      <c r="F181" s="11" t="n"/>
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>Swhetha Talreja</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="inlineStr">
+        <is>
+          <t>4+ years</t>
+        </is>
+      </c>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>Project Management and Digital Marketing Expert</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>Common Foundation</t>
+        </is>
+      </c>
+      <c r="E181" s="9" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="G181" s="11">
         <f>IF(F181="","",CHOOSE(F181,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
         <v/>
@@ -8795,8 +9334,14 @@
         <f>IF(F181="","",IF(I181="","Set target",IF(F181&gt;=I181,"Strong",IF(F181=I181-1,"Developing","Learning"))))</f>
         <v/>
       </c>
-      <c r="I181" s="11" t="n"/>
-      <c r="J181" s="10" t="n"/>
+      <c r="I181" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J181" s="10" t="inlineStr">
+        <is>
+          <t>Role-based starter rating; validate with team member</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="12" t="n"/>
@@ -9932,13 +10477,337 @@
       <c r="I244" s="14" t="n"/>
       <c r="J244" s="13" t="n"/>
     </row>
+    <row r="245">
+      <c r="A245" s="9" t="n"/>
+      <c r="B245" s="9" t="n"/>
+      <c r="C245" s="10" t="n"/>
+      <c r="D245" s="9" t="n"/>
+      <c r="E245" s="9" t="n"/>
+      <c r="F245" s="11" t="n"/>
+      <c r="G245" s="11">
+        <f>IF(F245="","",CHOOSE(F245,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H245" s="11">
+        <f>IF(F245="","",IF(I245="","Set target",IF(F245&gt;=I245,"Strong",IF(F245=I245-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I245" s="11" t="n"/>
+      <c r="J245" s="10" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="12" t="n"/>
+      <c r="B246" s="12" t="n"/>
+      <c r="C246" s="13" t="n"/>
+      <c r="D246" s="12" t="n"/>
+      <c r="E246" s="12" t="n"/>
+      <c r="F246" s="14" t="n"/>
+      <c r="G246" s="14">
+        <f>IF(F246="","",CHOOSE(F246,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H246" s="14">
+        <f>IF(F246="","",IF(I246="","Set target",IF(F246&gt;=I246,"Strong",IF(F246=I246-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I246" s="14" t="n"/>
+      <c r="J246" s="13" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="9" t="n"/>
+      <c r="B247" s="9" t="n"/>
+      <c r="C247" s="10" t="n"/>
+      <c r="D247" s="9" t="n"/>
+      <c r="E247" s="9" t="n"/>
+      <c r="F247" s="11" t="n"/>
+      <c r="G247" s="11">
+        <f>IF(F247="","",CHOOSE(F247,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H247" s="11">
+        <f>IF(F247="","",IF(I247="","Set target",IF(F247&gt;=I247,"Strong",IF(F247=I247-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I247" s="11" t="n"/>
+      <c r="J247" s="10" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="12" t="n"/>
+      <c r="B248" s="12" t="n"/>
+      <c r="C248" s="13" t="n"/>
+      <c r="D248" s="12" t="n"/>
+      <c r="E248" s="12" t="n"/>
+      <c r="F248" s="14" t="n"/>
+      <c r="G248" s="14">
+        <f>IF(F248="","",CHOOSE(F248,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H248" s="14">
+        <f>IF(F248="","",IF(I248="","Set target",IF(F248&gt;=I248,"Strong",IF(F248=I248-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I248" s="14" t="n"/>
+      <c r="J248" s="13" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="9" t="n"/>
+      <c r="B249" s="9" t="n"/>
+      <c r="C249" s="10" t="n"/>
+      <c r="D249" s="9" t="n"/>
+      <c r="E249" s="9" t="n"/>
+      <c r="F249" s="11" t="n"/>
+      <c r="G249" s="11">
+        <f>IF(F249="","",CHOOSE(F249,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H249" s="11">
+        <f>IF(F249="","",IF(I249="","Set target",IF(F249&gt;=I249,"Strong",IF(F249=I249-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I249" s="11" t="n"/>
+      <c r="J249" s="10" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="12" t="n"/>
+      <c r="B250" s="12" t="n"/>
+      <c r="C250" s="13" t="n"/>
+      <c r="D250" s="12" t="n"/>
+      <c r="E250" s="12" t="n"/>
+      <c r="F250" s="14" t="n"/>
+      <c r="G250" s="14">
+        <f>IF(F250="","",CHOOSE(F250,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H250" s="14">
+        <f>IF(F250="","",IF(I250="","Set target",IF(F250&gt;=I250,"Strong",IF(F250=I250-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I250" s="14" t="n"/>
+      <c r="J250" s="13" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="9" t="n"/>
+      <c r="B251" s="9" t="n"/>
+      <c r="C251" s="10" t="n"/>
+      <c r="D251" s="9" t="n"/>
+      <c r="E251" s="9" t="n"/>
+      <c r="F251" s="11" t="n"/>
+      <c r="G251" s="11">
+        <f>IF(F251="","",CHOOSE(F251,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H251" s="11">
+        <f>IF(F251="","",IF(I251="","Set target",IF(F251&gt;=I251,"Strong",IF(F251=I251-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I251" s="11" t="n"/>
+      <c r="J251" s="10" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="12" t="n"/>
+      <c r="B252" s="12" t="n"/>
+      <c r="C252" s="13" t="n"/>
+      <c r="D252" s="12" t="n"/>
+      <c r="E252" s="12" t="n"/>
+      <c r="F252" s="14" t="n"/>
+      <c r="G252" s="14">
+        <f>IF(F252="","",CHOOSE(F252,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H252" s="14">
+        <f>IF(F252="","",IF(I252="","Set target",IF(F252&gt;=I252,"Strong",IF(F252=I252-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I252" s="14" t="n"/>
+      <c r="J252" s="13" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="9" t="n"/>
+      <c r="B253" s="9" t="n"/>
+      <c r="C253" s="10" t="n"/>
+      <c r="D253" s="9" t="n"/>
+      <c r="E253" s="9" t="n"/>
+      <c r="F253" s="11" t="n"/>
+      <c r="G253" s="11">
+        <f>IF(F253="","",CHOOSE(F253,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H253" s="11">
+        <f>IF(F253="","",IF(I253="","Set target",IF(F253&gt;=I253,"Strong",IF(F253=I253-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I253" s="11" t="n"/>
+      <c r="J253" s="10" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="12" t="n"/>
+      <c r="B254" s="12" t="n"/>
+      <c r="C254" s="13" t="n"/>
+      <c r="D254" s="12" t="n"/>
+      <c r="E254" s="12" t="n"/>
+      <c r="F254" s="14" t="n"/>
+      <c r="G254" s="14">
+        <f>IF(F254="","",CHOOSE(F254,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H254" s="14">
+        <f>IF(F254="","",IF(I254="","Set target",IF(F254&gt;=I254,"Strong",IF(F254=I254-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I254" s="14" t="n"/>
+      <c r="J254" s="13" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="9" t="n"/>
+      <c r="B255" s="9" t="n"/>
+      <c r="C255" s="10" t="n"/>
+      <c r="D255" s="9" t="n"/>
+      <c r="E255" s="9" t="n"/>
+      <c r="F255" s="11" t="n"/>
+      <c r="G255" s="11">
+        <f>IF(F255="","",CHOOSE(F255,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H255" s="11">
+        <f>IF(F255="","",IF(I255="","Set target",IF(F255&gt;=I255,"Strong",IF(F255=I255-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I255" s="11" t="n"/>
+      <c r="J255" s="10" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="12" t="n"/>
+      <c r="B256" s="12" t="n"/>
+      <c r="C256" s="13" t="n"/>
+      <c r="D256" s="12" t="n"/>
+      <c r="E256" s="12" t="n"/>
+      <c r="F256" s="14" t="n"/>
+      <c r="G256" s="14">
+        <f>IF(F256="","",CHOOSE(F256,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H256" s="14">
+        <f>IF(F256="","",IF(I256="","Set target",IF(F256&gt;=I256,"Strong",IF(F256=I256-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I256" s="14" t="n"/>
+      <c r="J256" s="13" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="9" t="n"/>
+      <c r="B257" s="9" t="n"/>
+      <c r="C257" s="10" t="n"/>
+      <c r="D257" s="9" t="n"/>
+      <c r="E257" s="9" t="n"/>
+      <c r="F257" s="11" t="n"/>
+      <c r="G257" s="11">
+        <f>IF(F257="","",CHOOSE(F257,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H257" s="11">
+        <f>IF(F257="","",IF(I257="","Set target",IF(F257&gt;=I257,"Strong",IF(F257=I257-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I257" s="11" t="n"/>
+      <c r="J257" s="10" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="12" t="n"/>
+      <c r="B258" s="12" t="n"/>
+      <c r="C258" s="13" t="n"/>
+      <c r="D258" s="12" t="n"/>
+      <c r="E258" s="12" t="n"/>
+      <c r="F258" s="14" t="n"/>
+      <c r="G258" s="14">
+        <f>IF(F258="","",CHOOSE(F258,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H258" s="14">
+        <f>IF(F258="","",IF(I258="","Set target",IF(F258&gt;=I258,"Strong",IF(F258=I258-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I258" s="14" t="n"/>
+      <c r="J258" s="13" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="n"/>
+      <c r="B259" s="9" t="n"/>
+      <c r="C259" s="10" t="n"/>
+      <c r="D259" s="9" t="n"/>
+      <c r="E259" s="9" t="n"/>
+      <c r="F259" s="11" t="n"/>
+      <c r="G259" s="11">
+        <f>IF(F259="","",CHOOSE(F259,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H259" s="11">
+        <f>IF(F259="","",IF(I259="","Set target",IF(F259&gt;=I259,"Strong",IF(F259=I259-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I259" s="11" t="n"/>
+      <c r="J259" s="10" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="12" t="n"/>
+      <c r="B260" s="12" t="n"/>
+      <c r="C260" s="13" t="n"/>
+      <c r="D260" s="12" t="n"/>
+      <c r="E260" s="12" t="n"/>
+      <c r="F260" s="14" t="n"/>
+      <c r="G260" s="14">
+        <f>IF(F260="","",CHOOSE(F260,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H260" s="14">
+        <f>IF(F260="","",IF(I260="","Set target",IF(F260&gt;=I260,"Strong",IF(F260=I260-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I260" s="14" t="n"/>
+      <c r="J260" s="13" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="n"/>
+      <c r="B261" s="9" t="n"/>
+      <c r="C261" s="10" t="n"/>
+      <c r="D261" s="9" t="n"/>
+      <c r="E261" s="9" t="n"/>
+      <c r="F261" s="11" t="n"/>
+      <c r="G261" s="11">
+        <f>IF(F261="","",CHOOSE(F261,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H261" s="11">
+        <f>IF(F261="","",IF(I261="","Set target",IF(F261&gt;=I261,"Strong",IF(F261=I261-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I261" s="11" t="n"/>
+      <c r="J261" s="10" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="12" t="n"/>
+      <c r="B262" s="12" t="n"/>
+      <c r="C262" s="13" t="n"/>
+      <c r="D262" s="12" t="n"/>
+      <c r="E262" s="12" t="n"/>
+      <c r="F262" s="14" t="n"/>
+      <c r="G262" s="14">
+        <f>IF(F262="","",CHOOSE(F262,"Beginner","Basic","Intermediate","Advanced","Expert"))</f>
+        <v/>
+      </c>
+      <c r="H262" s="14">
+        <f>IF(F262="","",IF(I262="","Set target",IF(F262&gt;=I262,"Strong",IF(F262=I262-1,"Developing","Learning"))))</f>
+        <v/>
+      </c>
+      <c r="I262" s="14" t="n"/>
+      <c r="J262" s="13" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J244"/>
+  <autoFilter ref="A4:J262"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F244">
+  <conditionalFormatting sqref="F5:F262">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>1</formula>
     </cfRule>
@@ -9955,7 +10824,7 @@
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I244">
+  <conditionalFormatting sqref="I5:I262">
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
       <formula>1</formula>
     </cfRule>
@@ -9972,7 +10841,7 @@
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H244">
+  <conditionalFormatting sqref="H5:H262">
     <cfRule type="expression" priority="11" dxfId="5">
       <formula>H5="Strong"</formula>
     </cfRule>
@@ -9981,16 +10850,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="A5:A244" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown or leave this cell blank." promptTitle="Use the dropdown" prompt="Choose a prepared value for this field." type="list">
-      <formula1>=Lists!$A$2:$A$9</formula1>
+    <dataValidation sqref="A5:A262" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown or leave this cell blank." promptTitle="Use the dropdown" prompt="Choose a prepared value for this field." type="list">
+      <formula1>=Lists!$A$2:$A$10</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D244" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown or leave this cell blank." promptTitle="Use the dropdown" prompt="Choose a prepared value for this field." type="list">
-      <formula1>=Lists!$C$2:$C$36</formula1>
+    <dataValidation sqref="D5:D262" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown or leave this cell blank." promptTitle="Use the dropdown" prompt="Choose a prepared value for this field." type="list">
+      <formula1>=Lists!$C$2:$C$40</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E244" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown or leave this cell blank." promptTitle="Use the dropdown" prompt="Choose a prepared value for this field." type="list">
-      <formula1>=Lists!$B$2:$B$87</formula1>
+    <dataValidation sqref="E5:E262" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown or leave this cell blank." promptTitle="Use the dropdown" prompt="Choose a prepared value for this field." type="list">
+      <formula1>=Lists!$B$2:$B$95</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F244 I5:I244" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown or leave this cell blank." promptTitle="Use the dropdown" prompt="Choose a prepared value for this field." type="list">
+    <dataValidation sqref="F5:F262 I5:I262" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown or leave this cell blank." promptTitle="Use the dropdown" prompt="Choose a prepared value for this field." type="list">
       <formula1>=Lists!$D$2:$D$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -10119,7 +10988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10334,7 +11203,7 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Frameworks</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
@@ -10368,12 +11237,12 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>ServiceNow ITAM</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Asset Lifecycle Management</t>
+          <t>Application Deployment</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -10385,12 +11254,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Licensing</t>
+          <t>ServiceNow ITAM</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Atlassian / Oracle Licensing</t>
+          <t>Asset Lifecycle Management</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -10402,12 +11271,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Licensing</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Backlog Grooming</t>
+          <t>Atlassian / Oracle Licensing</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -10419,12 +11288,12 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>CI/CD</t>
+          <t>Backlog Grooming</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -10441,7 +11310,7 @@
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>CI/CD Pipeline Creation</t>
+          <t>CI/CD</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -10453,12 +11322,12 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>CI/CD Pipeline Creation</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -10470,12 +11339,12 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>CSS / SCSS</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -10487,12 +11356,12 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>Content Strategy</t>
+          <t>CSS / SCSS</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -10504,12 +11373,12 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>Cross-functional Leadership</t>
+          <t>Content Strategy</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -10521,12 +11390,12 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>Dashboards &amp; Reporting</t>
+          <t>Cross-functional Leadership</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -10538,12 +11407,12 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>Digital Marketing</t>
+          <t>Dashboards &amp; Reporting</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -10555,12 +11424,12 @@
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
@@ -10572,12 +11441,12 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>Express.js</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
@@ -10589,12 +11458,12 @@
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Electron.js</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
@@ -10606,12 +11475,12 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>End-to-End Frontend &amp; Backend Delivery</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
@@ -10623,12 +11492,12 @@
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Express.js</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
@@ -10640,12 +11509,12 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>Grafana</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -10657,12 +11526,12 @@
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Frontend System Architecture</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
@@ -10674,12 +11543,12 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>HTML5</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
@@ -10691,12 +11560,12 @@
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>SAM Implementation</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>Implementation &amp; Migration</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
@@ -10708,12 +11577,12 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>Discovery &amp; Inventory</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Jamf / Defender / InfraSecure</t>
+          <t>Grafana</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
@@ -10730,7 +11599,7 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -10742,12 +11611,12 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>HTML5</t>
         </is>
       </c>
       <c r="C37" s="16" t="inlineStr">
@@ -10759,12 +11628,12 @@
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Framework</t>
+          <t>SAM Implementation</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>Laravel Filament</t>
+          <t>Implementation &amp; Migration</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
@@ -10776,12 +11645,12 @@
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>Discovery &amp; Inventory</t>
         </is>
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>License Management</t>
+          <t>Jamf / Defender / InfraSecure</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
@@ -10793,12 +11662,12 @@
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>Common Foundation</t>
         </is>
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>License Optimization</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
@@ -10810,12 +11679,12 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Frameworks</t>
         </is>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>Marketing Analytics</t>
+          <t>JavaScript / TypeScript Frameworks &amp; Libraries</t>
         </is>
       </c>
       <c r="C41" s="16" t="inlineStr">
@@ -10827,12 +11696,12 @@
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>Micro Frontend</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
@@ -10844,12 +11713,12 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Framework</t>
         </is>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>Microservices Architecture</t>
+          <t>Laravel Filament</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
@@ -10861,12 +11730,12 @@
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Licensing</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>Microsoft Licensing</t>
+          <t>License Management</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
@@ -10878,12 +11747,12 @@
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>Module Federation</t>
+          <t>License Optimization</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
@@ -10895,12 +11764,12 @@
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Marketing Analytics</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
@@ -10912,12 +11781,12 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Micro Frontend</t>
         </is>
       </c>
       <c r="C47" s="16" t="inlineStr">
@@ -10929,12 +11798,12 @@
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Cloud / Hosting</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>Neon</t>
+          <t>Microservices Architecture</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
@@ -10946,12 +11815,12 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Licensing</t>
         </is>
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Microsoft Licensing</t>
         </is>
       </c>
       <c r="C49" s="16" t="inlineStr">
@@ -10963,12 +11832,12 @@
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>NgRx</t>
+          <t>Module Federation</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -10980,12 +11849,12 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>Node.js</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
@@ -10997,12 +11866,12 @@
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>PRD &amp; API Contract Writing</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
@@ -11014,12 +11883,12 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Cloud / Hosting</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Neon</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
@@ -11031,12 +11900,12 @@
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>Presentation Skills</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
@@ -11053,7 +11922,7 @@
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>PrimeNG</t>
+          <t>NgRx</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
@@ -11065,12 +11934,12 @@
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>Product Discovery</t>
+          <t>Node.js</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
@@ -11082,12 +11951,12 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>Project Planning</t>
+          <t>PRD &amp; API Contract Writing</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
@@ -11099,12 +11968,12 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
@@ -11116,12 +11985,12 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>REST APIs</t>
+          <t>Presentation Skills</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
@@ -11133,12 +12002,12 @@
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>RESTful APIs</t>
+          <t>PrimeNG</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
@@ -11150,12 +12019,12 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>React.js</t>
+          <t>Product Discovery</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
@@ -11167,12 +12036,12 @@
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>Redis</t>
+          <t>Project Planning</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
@@ -11184,12 +12053,12 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
@@ -11201,12 +12070,12 @@
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>API</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>RxJS</t>
+          <t>REST APIs</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
@@ -11218,12 +12087,12 @@
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>ServiceNow ITAM</t>
+          <t>API</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>SAM Pro</t>
+          <t>RESTful APIs</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
@@ -11235,12 +12104,12 @@
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Discovery &amp; Inventory</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>SCCM / Intune</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
@@ -11252,12 +12121,12 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>React.js</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
@@ -11274,7 +12143,7 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Redis</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
@@ -11286,12 +12155,12 @@
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Licensing</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>SaaS / FOSS Assessment</t>
+          <t>Responsive UI Development</t>
         </is>
       </c>
       <c r="C69" s="16" t="inlineStr">
@@ -11303,12 +12172,12 @@
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>ORM / Data</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>Sequelize</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
@@ -11320,12 +12189,12 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>Social Media Marketing</t>
+          <t>RxJS</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
@@ -11337,12 +12206,12 @@
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>ServiceNow ITAM</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>Software Compliance</t>
+          <t>SAM Pro</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
@@ -11354,12 +12223,12 @@
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Discovery &amp; Inventory</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>Sprint Planning</t>
+          <t>SCCM / Intune</t>
         </is>
       </c>
       <c r="C73" s="16" t="inlineStr">
@@ -11371,12 +12240,12 @@
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>Stakeholder Management</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
@@ -11388,12 +12257,12 @@
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Backend Services</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr">
@@ -11405,12 +12274,12 @@
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Licensing</t>
         </is>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>System Architecture</t>
+          <t>SaaS / FOSS Assessment</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
@@ -11422,12 +12291,12 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>ORM / Data</t>
         </is>
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>System Design</t>
+          <t>Sequelize</t>
         </is>
       </c>
       <c r="C77" s="16" t="inlineStr">
@@ -11439,12 +12308,12 @@
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Social Media Marketing</t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
@@ -11456,12 +12325,12 @@
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>Team Coordination</t>
+          <t>Software Compliance</t>
         </is>
       </c>
       <c r="C79" s="16" t="inlineStr">
@@ -11473,12 +12342,12 @@
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>Team Mentoring</t>
+          <t>Sprint Planning</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
@@ -11490,12 +12359,12 @@
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>Technical Debt Management</t>
+          <t>Stakeholder Management</t>
         </is>
       </c>
       <c r="C81" s="16" t="inlineStr">
@@ -11507,12 +12376,12 @@
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Backend Services</t>
         </is>
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>Technical Documentation</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
@@ -11524,12 +12393,12 @@
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>Common Foundation</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>System Architecture</t>
         </is>
       </c>
       <c r="C83" s="16" t="inlineStr">
@@ -11541,12 +12410,12 @@
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>UAT / Process / Go-Live</t>
+          <t>System Design</t>
         </is>
       </c>
       <c r="C84" s="16" t="inlineStr">
@@ -11558,12 +12427,12 @@
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="C85" s="16" t="inlineStr">
@@ -11575,12 +12444,12 @@
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>AI / Automation</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>Web Scraping</t>
+          <t>Team Coordination</t>
         </is>
       </c>
       <c r="C86" s="16" t="inlineStr">
@@ -11592,22 +12461,158 @@
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>Team Mentoring</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>Technical Debt Management</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>Technical Documentation</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Common Foundation</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="B91" s="16" t="inlineStr">
+        <is>
+          <t>UAT / Process / Go-Live</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>Vercel</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="B93" s="16" t="inlineStr">
+        <is>
+          <t>Web Application Development</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>AI / Automation</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Web Scraping</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
           <t>Product Management</t>
         </is>
       </c>
-      <c r="B87" s="16" t="inlineStr">
+      <c r="B95" s="16" t="inlineStr">
         <is>
           <t>Workflow Orchestration</t>
         </is>
       </c>
-      <c r="C87" s="16" t="inlineStr">
+      <c r="C95" s="16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C87"/>
+  <autoFilter ref="A1:C95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12105,7 +13110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D87"/>
+  <dimension ref="A2:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -12131,7 +13136,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kajal Mahapatra</t>
+          <t>MD Salman</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12151,7 +13156,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Subham Sahoo</t>
+          <t>Kajal Mahapatra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12171,7 +13176,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gautam Kumar</t>
+          <t>Subham Sahoo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -12191,7 +13196,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rajat Mahapatra</t>
+          <t>Gautam Kumar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -12211,7 +13216,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sohail amjad</t>
+          <t>Rajat Mahapatra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -12228,7 +13233,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Suraj Sharma</t>
+          <t>Sohail amjad</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12245,21 +13250,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Suraj Sharma</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Administration &amp; Configuration</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Swhetha Talreja</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Administration &amp; Configuration</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
       <c r="B10" t="inlineStr">
         <is>
           <t>Adobe Licensing</t>
@@ -12322,7 +13332,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Asset Lifecycle Management</t>
+          <t>Application Deployment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -12334,7 +13344,7 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Atlassian / Oracle Licensing</t>
+          <t>Asset Lifecycle Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12346,595 +13356,671 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Backlog Grooming</t>
+          <t>Atlassian / Oracle Licensing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Delivery</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>CI/CD</t>
+          <t>Backlog Grooming</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Deployment</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>CI/CD Pipeline Creation</t>
+          <t>CI/CD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Discovery &amp; Inventory</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>CI/CD Pipeline Creation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>DevOps</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>CSS / SCSS</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Framework</t>
+          <t>Discovery &amp; Inventory</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Content Strategy</t>
+          <t>CSS / SCSS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Documentation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cross-functional Leadership</t>
+          <t>Content Strategy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Framework</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dashboards &amp; Reporting</t>
+          <t>Cross-functional Leadership</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Frameworks</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Digital Marketing</t>
+          <t>Dashboards &amp; Reporting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Licensing</t>
+          <t>Frontend</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Languages</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>Express.js</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Electron.js</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ORM / Data</t>
+          <t>Licensing</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>End-to-End Frontend &amp; Backend Delivery</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Express.js</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grafana</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Monitoring</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Frontend System Architecture</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>ORM / Data</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>HTML5</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SAM Implementation</t>
+          <t>Product Management</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Implementation &amp; Migration</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ServiceNow ITAM</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jamf / Defender / InfraSecure</t>
+          <t>Grafana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ServiceNow Platform</t>
+          <t>Reporting</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>SAM</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>HTML5</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SAM Implementation</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>Laravel Filament</t>
+          <t>Implementation &amp; Migration</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ServiceNow ITAM</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>License Management</t>
+          <t>Jamf / Defender / InfraSecure</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ServiceNow Platform</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>License Optimization</t>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tools</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>Marketing Analytics</t>
+          <t>JavaScript / TypeScript Frameworks &amp; Libraries</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>Micro Frontend</t>
+          <t>Kibana</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>Microservices Architecture</t>
+          <t>Laravel Filament</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>Microsoft Licensing</t>
+          <t>License Management</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>Module Federation</t>
+          <t>License Optimization</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Marketing Analytics</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Micro Frontend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>Neon</t>
+          <t>Microservices Architecture</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Microsoft Licensing</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>NgRx</t>
+          <t>Module Federation</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>Node.js</t>
+          <t>MongoDB</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>PRD &amp; API Contract Writing</t>
+          <t>MySQL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Neon</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>Presentation Skills</t>
+          <t>Next.js</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>PrimeNG</t>
+          <t>NgRx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>Product Discovery</t>
+          <t>Node.js</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>Project Planning</t>
+          <t>PRD &amp; API Contract Writing</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>REST APIs</t>
+          <t>Presentation Skills</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>RESTful APIs</t>
+          <t>PrimeNG</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>React.js</t>
+          <t>Product Discovery</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>Redis</t>
+          <t>Project Planning</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>RxJS</t>
+          <t>REST APIs</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>SAM Pro</t>
+          <t>RESTful APIs</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>SCCM / Intune</t>
+          <t>React Native</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>React.js</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Redis</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>SaaS / FOSS Assessment</t>
+          <t>Responsive UI Development</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sequelize</t>
+          <t>Risk Management</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>Social Media Marketing</t>
+          <t>RxJS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>Software Compliance</t>
+          <t>SAM Pro</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sprint Planning</t>
+          <t>SCCM / Intune</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>Stakeholder Management</t>
+          <t>SEO</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>SQL</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>System Architecture</t>
+          <t>SaaS / FOSS Assessment</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>System Design</t>
+          <t>Sequelize</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Social Media Marketing</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>Team Coordination</t>
+          <t>Software Compliance</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>Team Mentoring</t>
+          <t>Sprint Planning</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>Technical Debt Management</t>
+          <t>Stakeholder Management</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>Technical Documentation</t>
+          <t>Supabase</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>System Architecture</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t>UAT / Process / Go-Live</t>
+          <t>System Design</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>System Scalability</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>Web Scraping</t>
+          <t>Team Coordination</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
+        <is>
+          <t>Team Mentoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Technical Debt Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Technical Documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>UAT / Process / Go-Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Vercel</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Web Application Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Web Scraping</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Workflow Orchestration</t>
         </is>
